--- a/リメンバーミー_FI動静表.xlsx
+++ b/リメンバーミー_FI動静表.xlsx
@@ -1011,8 +1011,16 @@
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>山下</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>村瀬</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
@@ -2648,8 +2656,16 @@
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>山下</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>村瀬</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4544,8 +4560,16 @@
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>山下</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>村瀬</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
@@ -6366,7 +6390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D37"/>
+  <dimension ref="B2:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6576,88 +6600,92 @@
     <row r="16">
       <c r="B16" s="70" t="inlineStr">
         <is>
-          <t>会場</t>
+          <t>美術</t>
         </is>
       </c>
       <c r="C16" s="71" t="inlineStr">
         <is>
-          <t>SHIBUYA109広告メディア・イベントスペース事務局　上村様</t>
+          <t>山下さん</t>
         </is>
       </c>
       <c r="D16" s="71" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="69" t="inlineStr">
-        <is>
-          <t>■ 控室</t>
-        </is>
-      </c>
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>テクニカル</t>
+        </is>
+      </c>
+      <c r="C17" s="71" t="inlineStr">
+        <is>
+          <t>村瀬さん</t>
+        </is>
+      </c>
+      <c r="D17" s="71" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="70" t="inlineStr">
         <is>
-          <t>控室①</t>
+          <t>会場</t>
         </is>
       </c>
       <c r="C18" s="71" t="inlineStr">
         <is>
-          <t>SHIBUYA109 屋上控室（BANDAI SPIRITS様控室）</t>
-        </is>
-      </c>
-      <c r="D18" s="71" t="inlineStr">
-        <is>
-          <t>1F搬入口よりEVで9階→屋上へ出て外階段から入室</t>
-        </is>
-      </c>
+          <t>SHIBUYA109広告メディア・イベントスペース事務局　上村様</t>
+        </is>
+      </c>
+      <c r="D18" s="71" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="70" t="inlineStr">
-        <is>
-          <t>控室②</t>
-        </is>
-      </c>
-      <c r="C19" s="71" t="inlineStr">
-        <is>
-          <t>AP貸し会議室 13F Eルーム（運営控室・備品保管・ストックルーム）</t>
-        </is>
-      </c>
-      <c r="D19" s="71" t="inlineStr">
-        <is>
-          <t>東京都渋谷区道玄坂2-6-17 渋東シネタワー13F（受付13F）※会場ななめ向かいTOHOシネマズのビル</t>
+      <c r="B19" s="69" t="inlineStr">
+        <is>
+          <t>■ 控室</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="70" t="inlineStr">
         <is>
+          <t>控室①</t>
+        </is>
+      </c>
+      <c r="C20" s="71" t="inlineStr">
+        <is>
+          <t>SHIBUYA109 屋上控室（BANDAI SPIRITS様控室）</t>
+        </is>
+      </c>
+      <c r="D20" s="71" t="inlineStr">
+        <is>
+          <t>1F搬入口よりEVで9階→屋上へ出て外階段から入室</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="70" t="inlineStr">
+        <is>
+          <t>控室②</t>
+        </is>
+      </c>
+      <c r="C21" s="71" t="inlineStr">
+        <is>
+          <t>AP貸し会議室 13F Eルーム（運営控室・備品保管・ストックルーム）</t>
+        </is>
+      </c>
+      <c r="D21" s="71" t="inlineStr">
+        <is>
+          <t>東京都渋谷区道玄坂2-6-17 渋東シネタワー13F（受付13F）※会場ななめ向かいTOHOシネマズのビル</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="70" t="inlineStr">
+        <is>
           <t>控室② 利用時間</t>
         </is>
       </c>
-      <c r="C20" s="71" t="inlineStr">
+      <c r="C22" s="71" t="inlineStr">
         <is>
           <t>10/29　19:00-22:00</t>
-        </is>
-      </c>
-      <c r="D20" s="71" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="70" t="inlineStr"/>
-      <c r="C21" s="71" t="inlineStr">
-        <is>
-          <t>10/30　9:00-22:00</t>
-        </is>
-      </c>
-      <c r="D21" s="72" t="inlineStr">
-        <is>
-          <t>※未定。借りっぱなしで9:00〜のままの契約でOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="70" t="inlineStr"/>
-      <c r="C22" s="71" t="inlineStr">
-        <is>
-          <t>10/31　7:00-21:00</t>
         </is>
       </c>
       <c r="D22" s="71" t="inlineStr"/>
@@ -6666,112 +6694,108 @@
       <c r="B23" s="70" t="inlineStr"/>
       <c r="C23" s="71" t="inlineStr">
         <is>
+          <t>10/30　9:00-22:00</t>
+        </is>
+      </c>
+      <c r="D23" s="72" t="inlineStr">
+        <is>
+          <t>※未定。借りっぱなしで9:00〜のままの契約でOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="70" t="inlineStr"/>
+      <c r="C24" s="71" t="inlineStr">
+        <is>
+          <t>10/31　7:00-21:00</t>
+        </is>
+      </c>
+      <c r="D24" s="71" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="70" t="inlineStr"/>
+      <c r="C25" s="71" t="inlineStr">
+        <is>
           <t>11/1　7:00-22:00</t>
         </is>
       </c>
-      <c r="D23" s="72" t="inlineStr">
+      <c r="D25" s="72" t="inlineStr">
         <is>
           <t>※撤去作業(〜23:00)との兼ね合い要確認</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="69" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="69" t="inlineStr">
         <is>
           <t>■ 道路使用許可</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="70" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="70" t="inlineStr">
         <is>
           <t>搬入</t>
         </is>
       </c>
-      <c r="C25" s="71" t="inlineStr">
+      <c r="C27" s="71" t="inlineStr">
         <is>
           <t>10/29(木) 21:00〜24:00</t>
         </is>
       </c>
-      <c r="D25" s="71" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="70" t="inlineStr">
-        <is>
-          <t>搬出</t>
-        </is>
-      </c>
-      <c r="C26" s="71" t="inlineStr">
-        <is>
-          <t>11/1(日) 21:00〜24:00</t>
-        </is>
-      </c>
-      <c r="D26" s="71" t="inlineStr">
-        <is>
-          <t>※今後変更可能性あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="69" t="inlineStr">
-        <is>
-          <t>■ リース（牧野リース）</t>
-        </is>
-      </c>
+      <c r="D27" s="71" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="70" t="inlineStr">
         <is>
+          <t>搬出</t>
+        </is>
+      </c>
+      <c r="C28" s="71" t="inlineStr">
+        <is>
+          <t>11/1(日) 21:00〜24:00</t>
+        </is>
+      </c>
+      <c r="D28" s="71" t="inlineStr">
+        <is>
+          <t>※今後変更可能性あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="69" t="inlineStr">
+        <is>
+          <t>■ リース（牧野リース）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="70" t="inlineStr">
+        <is>
           <t>借用期間</t>
         </is>
       </c>
-      <c r="C28" s="71" t="inlineStr">
+      <c r="C30" s="71" t="inlineStr">
         <is>
           <t>10/29(木)21:00 〜 11/1(日)24:00</t>
         </is>
       </c>
-      <c r="D28" s="71" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="70" t="inlineStr">
+      <c r="D30" s="71" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="70" t="inlineStr">
         <is>
           <t>借用内容</t>
         </is>
       </c>
-      <c r="C29" s="71" t="inlineStr">
+      <c r="C31" s="71" t="inlineStr">
         <is>
           <t>PS-36B サインスタンド</t>
         </is>
       </c>
-      <c r="D29" s="71" t="inlineStr">
+      <c r="D31" s="71" t="inlineStr">
         <is>
           <t>×10</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="70" t="inlineStr"/>
-      <c r="C30" s="71" t="inlineStr">
-        <is>
-          <t>PS-86 カタログスタンド</t>
-        </is>
-      </c>
-      <c r="D30" s="71" t="inlineStr">
-        <is>
-          <t>×1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="70" t="inlineStr"/>
-      <c r="C31" s="71" t="inlineStr">
-        <is>
-          <t>PP-51E ベルトパーテーション</t>
-        </is>
-      </c>
-      <c r="D31" s="71" t="inlineStr">
-        <is>
-          <t>×30</t>
         </is>
       </c>
     </row>
@@ -6779,58 +6803,84 @@
       <c r="B32" s="70" t="inlineStr"/>
       <c r="C32" s="71" t="inlineStr">
         <is>
+          <t>PS-86 カタログスタンド</t>
+        </is>
+      </c>
+      <c r="D32" s="71" t="inlineStr">
+        <is>
+          <t>×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="70" t="inlineStr"/>
+      <c r="C33" s="71" t="inlineStr">
+        <is>
+          <t>PP-51E ベルトパーテーション</t>
+        </is>
+      </c>
+      <c r="D33" s="71" t="inlineStr">
+        <is>
+          <t>×30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="70" t="inlineStr"/>
+      <c r="C34" s="71" t="inlineStr">
+        <is>
           <t>カタログスタンド・サインスタンド用ウェイト</t>
         </is>
       </c>
-      <c r="D32" s="71" t="inlineStr">
+      <c r="D34" s="71" t="inlineStr">
         <is>
           <t>×10</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="69" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="69" t="inlineStr">
         <is>
           <t>■ お弁当</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="70" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="70" t="inlineStr">
         <is>
           <t>搬入</t>
         </is>
       </c>
-      <c r="C34" s="71" t="inlineStr">
+      <c r="C36" s="71" t="inlineStr">
         <is>
           <t>10/31・11/1 両日 11:00</t>
         </is>
       </c>
-      <c r="D34" s="71" t="inlineStr">
+      <c r="D36" s="71" t="inlineStr">
         <is>
           <t>※現在の想定</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="70" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="70" t="inlineStr">
         <is>
           <t>回収</t>
         </is>
       </c>
-      <c r="C35" s="71" t="inlineStr">
+      <c r="C37" s="71" t="inlineStr">
         <is>
           <t>10/31・11/1 両日 15:00〜16:00</t>
         </is>
       </c>
-      <c r="D35" s="71" t="inlineStr">
+      <c r="D37" s="71" t="inlineStr">
         <is>
           <t>※現在の想定</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="73" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="73" t="inlineStr">
         <is>
           <t>※出典：実施概要・施工/本番スケジュール資料、及び共有情報（道路使用・リース・控室・弁当）</t>
         </is>
@@ -6838,11 +6888,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
